--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FLEXICAR FUENLABRADA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FLEXICAR FUENLABRADA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA ALCOLADO</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>40.011</v>
+        <v>43.4134</v>
       </c>
       <c r="E2" t="n">
-        <v>32.1359</v>
+        <v>28.0492</v>
       </c>
       <c r="F2" t="n">
-        <v>7.8751</v>
+        <v>15.3642</v>
       </c>
       <c r="G2" t="n">
-        <v>16.0045</v>
+        <v>38.0376</v>
       </c>
       <c r="H2" t="n">
-        <v>15.309</v>
+        <v>16.2801</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6952999999999998</v>
+        <v>21.7579</v>
       </c>
       <c r="J2" t="n">
-        <v>24.5191</v>
+        <v>78.36960000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>16.8877</v>
+        <v>29.5291</v>
       </c>
       <c r="L2" t="n">
-        <v>7.6315</v>
+        <v>48.8405</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.5146</v>
+        <v>-40.3319</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5783</v>
+        <v>-13.2489</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.9361</v>
+        <v>-27.0829</v>
       </c>
       <c r="P2" t="n">
-        <v>-10.8753</v>
+        <v>-22.4031</v>
       </c>
       <c r="Q2" t="n">
-        <v>-24.7959</v>
+        <v>-84.3926</v>
       </c>
       <c r="R2" t="n">
-        <v>13.9203</v>
+        <v>61.9896</v>
       </c>
       <c r="S2" t="n">
-        <v>24.6501</v>
+        <v>-0.008299999999999863</v>
       </c>
       <c r="T2" t="n">
-        <v>18.01</v>
+        <v>-12.3808</v>
       </c>
       <c r="U2" t="n">
-        <v>6.64</v>
+        <v>12.3724</v>
       </c>
       <c r="V2" t="n">
-        <v>10.2318</v>
+        <v>27.7876</v>
       </c>
       <c r="W2" t="n">
-        <v>14.4027</v>
+        <v>46.453</v>
       </c>
       <c r="X2" t="n">
-        <v>-4.1708</v>
+        <v>-18.6658</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>32.3295</v>
+        <v>32.0029</v>
       </c>
       <c r="E3" t="n">
-        <v>15.4713</v>
+        <v>21.0317</v>
       </c>
       <c r="F3" t="n">
-        <v>16.8589</v>
+        <v>10.9713</v>
       </c>
       <c r="G3" t="n">
-        <v>38.0376</v>
+        <v>37.7785</v>
       </c>
       <c r="H3" t="n">
-        <v>16.2801</v>
+        <v>5.696900000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>21.7579</v>
+        <v>32.0821</v>
       </c>
       <c r="J3" t="n">
-        <v>78.36960000000001</v>
+        <v>72.14360000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>29.5291</v>
+        <v>16.585</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8405</v>
+        <v>55.5586</v>
       </c>
       <c r="M3" t="n">
-        <v>-40.3319</v>
+        <v>-34.3646</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.2489</v>
+        <v>-10.8883</v>
       </c>
       <c r="O3" t="n">
-        <v>-27.0829</v>
+        <v>-23.4766</v>
       </c>
       <c r="P3" t="n">
-        <v>-22.4031</v>
+        <v>-18.9233</v>
       </c>
       <c r="Q3" t="n">
-        <v>-84.3926</v>
+        <v>-76.34480000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>61.9896</v>
+        <v>57.4217</v>
       </c>
       <c r="S3" t="n">
-        <v>-11.0923</v>
+        <v>-7.5847</v>
       </c>
       <c r="T3" t="n">
-        <v>-24.9587</v>
+        <v>-13.2893</v>
       </c>
       <c r="U3" t="n">
-        <v>13.8669</v>
+        <v>5.704400000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>27.7876</v>
+        <v>20.7323</v>
       </c>
       <c r="W3" t="n">
-        <v>46.453</v>
+        <v>38.5227</v>
       </c>
       <c r="X3" t="n">
-        <v>-18.6658</v>
+        <v>-17.7903</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ALI</t>
+          <t>I. AURRECOECHEA ALCOLADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>16.2527</v>
+        <v>26.0067</v>
       </c>
       <c r="E4" t="n">
-        <v>10.3812</v>
+        <v>20.0733</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8714</v>
+        <v>5.9333</v>
       </c>
       <c r="G4" t="n">
-        <v>9.474400000000001</v>
+        <v>16.0045</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6773</v>
+        <v>15.309</v>
       </c>
       <c r="I4" t="n">
-        <v>5.797099999999999</v>
+        <v>0.6952999999999998</v>
       </c>
       <c r="J4" t="n">
-        <v>15.8846</v>
+        <v>24.5191</v>
       </c>
       <c r="K4" t="n">
-        <v>7.578200000000001</v>
+        <v>16.8877</v>
       </c>
       <c r="L4" t="n">
-        <v>8.3064</v>
+        <v>7.6315</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.410299999999999</v>
+        <v>-8.5146</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.9007</v>
+        <v>-1.5783</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.5095</v>
+        <v>-6.9361</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9574</v>
+        <v>-10.8753</v>
       </c>
       <c r="Q4" t="n">
-        <v>-11.3103</v>
+        <v>-24.7959</v>
       </c>
       <c r="R4" t="n">
-        <v>9.3528</v>
+        <v>13.9203</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2388</v>
+        <v>10.6458</v>
       </c>
       <c r="T4" t="n">
-        <v>-4.9486</v>
+        <v>5.9474</v>
       </c>
       <c r="U4" t="n">
-        <v>3.7099</v>
+        <v>4.6985</v>
       </c>
       <c r="V4" t="n">
-        <v>9.974499999999999</v>
+        <v>10.2318</v>
       </c>
       <c r="W4" t="n">
-        <v>10.7554</v>
+        <v>14.4027</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7809999999999998</v>
+        <v>-4.1708</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>P. ALI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>11.4209</v>
+        <v>18.8935</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5344</v>
+        <v>13.0886</v>
       </c>
       <c r="F5" t="n">
-        <v>3.886400000000001</v>
+        <v>5.8047</v>
       </c>
       <c r="G5" t="n">
-        <v>37.7785</v>
+        <v>9.474400000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>5.696900000000001</v>
+        <v>3.6773</v>
       </c>
       <c r="I5" t="n">
-        <v>32.0821</v>
+        <v>5.797099999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>72.14360000000001</v>
+        <v>15.8846</v>
       </c>
       <c r="K5" t="n">
-        <v>16.585</v>
+        <v>7.578200000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>55.5586</v>
+        <v>8.3064</v>
       </c>
       <c r="M5" t="n">
-        <v>-34.3646</v>
+        <v>-6.410299999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.8883</v>
+        <v>-3.9007</v>
       </c>
       <c r="O5" t="n">
-        <v>-23.4766</v>
+        <v>-2.5095</v>
       </c>
       <c r="P5" t="n">
-        <v>-18.9233</v>
+        <v>-1.9574</v>
       </c>
       <c r="Q5" t="n">
-        <v>-76.34480000000001</v>
+        <v>-11.3103</v>
       </c>
       <c r="R5" t="n">
-        <v>57.4217</v>
+        <v>9.3528</v>
       </c>
       <c r="S5" t="n">
-        <v>-28.1668</v>
+        <v>1.4021</v>
       </c>
       <c r="T5" t="n">
-        <v>-26.7862</v>
+        <v>-2.2411</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3802</v>
+        <v>3.6432</v>
       </c>
       <c r="V5" t="n">
-        <v>20.7323</v>
+        <v>9.974499999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>38.5227</v>
+        <v>10.7554</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.7903</v>
+        <v>-0.7809999999999998</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>5.6357</v>
+        <v>6.757099999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7067</v>
+        <v>6.658500000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07089999999999985</v>
+        <v>0.09859999999999991</v>
       </c>
       <c r="G6" t="n">
         <v>1.2944</v>
@@ -922,13 +922,13 @@
         <v>12.6153</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.4428</v>
+        <v>-2.3213</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.2698</v>
+        <v>-2.3179</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1731</v>
+        <v>-0.003500000000000059</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6986999999999999</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>5.3916</v>
+        <v>0.3068000000000017</v>
       </c>
       <c r="E7" t="n">
-        <v>9.9825</v>
+        <v>-1.986400000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.591000000000001</v>
+        <v>2.2932</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.096299999999999</v>
+        <v>5.735899999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>6.895500000000001</v>
+        <v>0.8286000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-12.9917</v>
+        <v>4.907</v>
       </c>
       <c r="J7" t="n">
-        <v>26.9318</v>
+        <v>27.0802</v>
       </c>
       <c r="K7" t="n">
-        <v>19.0166</v>
+        <v>11.0624</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9153</v>
+        <v>16.0174</v>
       </c>
       <c r="M7" t="n">
-        <v>-33.0283</v>
+        <v>-21.3446</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.1205</v>
+        <v>-10.2342</v>
       </c>
       <c r="O7" t="n">
-        <v>-20.9072</v>
+        <v>-11.1104</v>
       </c>
       <c r="P7" t="n">
-        <v>-14.1382</v>
+        <v>-7.1779</v>
       </c>
       <c r="Q7" t="n">
-        <v>-52.4188</v>
+        <v>-39.3685</v>
       </c>
       <c r="R7" t="n">
-        <v>38.281</v>
+        <v>32.1905</v>
       </c>
       <c r="S7" t="n">
-        <v>16.5115</v>
+        <v>5.0155</v>
       </c>
       <c r="T7" t="n">
-        <v>9.0372</v>
+        <v>-1.0596</v>
       </c>
       <c r="U7" t="n">
-        <v>7.474600000000001</v>
+        <v>6.0752</v>
       </c>
       <c r="V7" t="n">
-        <v>9.1144</v>
+        <v>-3.2669</v>
       </c>
       <c r="W7" t="n">
-        <v>26.4326</v>
+        <v>11.3618</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.3186</v>
+        <v>-14.6287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02439999999999864</v>
+        <v>-0.0335</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.3157</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5.340000000000001</v>
+        <v>-0.0335</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.2278</v>
+        <v>-0.0335</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6537</v>
+        <v>-0.1825</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.574</v>
+        <v>0.149</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8506999999999998</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08390000000000009</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7665000000000001</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.0784</v>
+        <v>-0.0335</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7378</v>
+        <v>-0.1825</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.3408</v>
+        <v>0.149</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9576</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.0053</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>8.047699999999999</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>6.1243</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2772</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.8471</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.0853</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5617</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5237000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>A. RUPÉREZ VÁZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,43 +1108,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0335</v>
+        <v>-0.1092</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0335</v>
+        <v>-0.1475</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0335</v>
+        <v>0.2693</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1825</v>
+        <v>-0.06699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.149</v>
+        <v>0.3363</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0335</v>
+        <v>0.231</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1825</v>
+        <v>-0.06699999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.149</v>
+        <v>0.298</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.3785</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.3785</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RUPÉREZ VÁZQUEZ</t>
+          <t>A. GOMEZ FRAILE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,43 +1186,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1092</v>
+        <v>-1.3816</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0382</v>
+        <v>-0.9443</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1475</v>
+        <v>-0.4373</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2693</v>
+        <v>-1.3867</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.06699999999999999</v>
+        <v>-1.256</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3363</v>
+        <v>-0.1307</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0382</v>
+        <v>-0.6703</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.7086</v>
       </c>
       <c r="L10" t="n">
         <v>0.0382</v>
       </c>
       <c r="M10" t="n">
-        <v>0.231</v>
+        <v>-0.7164</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06699999999999999</v>
+        <v>-0.5475</v>
       </c>
       <c r="O10" t="n">
-        <v>0.298</v>
+        <v>-0.1689</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3785</v>
+        <v>0.005099999999999993</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.274</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3785</v>
+        <v>0.2791</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GOMEZ FRAILE</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2275</v>
+        <v>-2.8644</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9443</v>
+        <v>-6.7866</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2832</v>
+        <v>3.9221</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3867</v>
+        <v>-6.2278</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.256</v>
+        <v>-1.6537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1307</v>
+        <v>-4.574</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6703</v>
+        <v>0.8506999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7086</v>
+        <v>0.08390000000000009</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0382</v>
+        <v>0.7665000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7164</v>
+        <v>-7.0784</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5475</v>
+        <v>-1.7378</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1689</v>
+        <v>-5.3408</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-10.0053</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>8.047699999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1592</v>
+        <v>3.2354</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.274</v>
+        <v>0.8064</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4332</v>
+        <v>2.4292</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.0853</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5617</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.5237000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.61</v>
+        <v>-4.222200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8664999999999998</v>
+        <v>-4.1729</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7435</v>
+        <v>-0.04930000000000057</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9304</v>
+        <v>3.8375</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1589</v>
+        <v>-0.2255</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7714</v>
+        <v>4.063</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2297</v>
+        <v>1.1546</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0365</v>
+        <v>-1.1801</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2662</v>
+        <v>2.3346</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7007</v>
+        <v>2.6826</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1954</v>
+        <v>0.9541999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5053</v>
+        <v>1.728</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.3925</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2175</v>
+        <v>-5.654999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2175</v>
+        <v>3.2625</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5496</v>
+        <v>-0.1919000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4194</v>
+        <v>0.1323</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1304</v>
+        <v>-0.3240000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>-5.4754</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>-5.670599999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8043</v>
+        <v>-4.3878</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2414</v>
+        <v>-0.9781999999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5632000000000003</v>
+        <v>-3.4095</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8375</v>
+        <v>-2.9304</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2255</v>
+        <v>-1.1589</v>
       </c>
       <c r="I13" t="n">
-        <v>4.063</v>
+        <v>-1.7714</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1546</v>
+        <v>-0.2297</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1801</v>
+        <v>0.0365</v>
       </c>
       <c r="L13" t="n">
-        <v>2.3346</v>
+        <v>-0.2662</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6826</v>
+        <v>-2.7007</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9541999999999999</v>
+        <v>-1.1954</v>
       </c>
       <c r="O13" t="n">
-        <v>1.728</v>
+        <v>-1.5053</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.3925</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.654999999999999</v>
+        <v>-0.2175</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2625</v>
+        <v>0.2175</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7744000000000001</v>
+        <v>-0.3275</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06369999999999985</v>
+        <v>-0.5311</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8381000000000001</v>
+        <v>0.2037</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.4754</v>
+        <v>-1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.670599999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.3347</v>
+        <v>-4.83</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.2356</v>
+        <v>-0.2703000000000007</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9005999999999993</v>
+        <v>-4.5595</v>
       </c>
       <c r="G14" t="n">
-        <v>5.735899999999999</v>
+        <v>-6.096299999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8286000000000001</v>
+        <v>6.895500000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>4.907</v>
+        <v>-12.9917</v>
       </c>
       <c r="J14" t="n">
-        <v>27.0802</v>
+        <v>26.9318</v>
       </c>
       <c r="K14" t="n">
-        <v>11.0624</v>
+        <v>19.0166</v>
       </c>
       <c r="L14" t="n">
-        <v>16.0174</v>
+        <v>7.9153</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.3446</v>
+        <v>-33.0283</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.2342</v>
+        <v>-12.1205</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.1104</v>
+        <v>-20.9072</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.1779</v>
+        <v>-14.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-39.3685</v>
+        <v>-52.4188</v>
       </c>
       <c r="R14" t="n">
-        <v>32.1905</v>
+        <v>38.281</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6257</v>
+        <v>6.29</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.3088</v>
+        <v>-1.2162</v>
       </c>
       <c r="U14" t="n">
-        <v>4.6829</v>
+        <v>7.5057</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.2669</v>
+        <v>9.1144</v>
       </c>
       <c r="W14" t="n">
-        <v>11.3618</v>
+        <v>26.4326</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.6287</v>
+        <v>-17.3186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. MARTIN</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.366</v>
+        <v>-7.219399999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.254399999999999</v>
+        <v>-5.847099999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.111700000000001</v>
+        <v>-1.371800000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.8382</v>
+        <v>8.363099999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.1768</v>
+        <v>16.1998</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6616</v>
+        <v>-7.836299999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4035000000000004</v>
+        <v>48.1573</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.3192</v>
+        <v>32.1643</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9156</v>
+        <v>15.9929</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.4346</v>
+        <v>-39.7941</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.8573</v>
+        <v>-15.9649</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.5772</v>
+        <v>-23.8295</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.5677</v>
+        <v>-0.652499999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-10.8753</v>
+        <v>-59.3791</v>
       </c>
       <c r="R15" t="n">
-        <v>6.3075</v>
+        <v>58.7268</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8891</v>
+        <v>-5.5754</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5286</v>
+        <v>-9.7585</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3606</v>
+        <v>4.1833</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1506</v>
+        <v>-9.354699999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>5.496</v>
+        <v>15.133</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.3454</v>
+        <v>-24.4878</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>C. MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.6312</v>
+        <v>-11.6879</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.3818</v>
+        <v>-6.712999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>4.750300000000002</v>
+        <v>-4.9748</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6051</v>
+        <v>-7.8382</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.021599999999999</v>
+        <v>-6.1768</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5829</v>
+        <v>-1.6616</v>
       </c>
       <c r="J16" t="n">
-        <v>14.7424</v>
+        <v>-0.4035000000000004</v>
       </c>
       <c r="K16" t="n">
-        <v>4.087499999999999</v>
+        <v>-2.3192</v>
       </c>
       <c r="L16" t="n">
-        <v>10.6546</v>
+        <v>1.9156</v>
       </c>
       <c r="M16" t="n">
-        <v>-17.3471</v>
+        <v>-7.4346</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.1092</v>
+        <v>-3.8573</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.2379</v>
+        <v>-3.5772</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7402</v>
+        <v>-4.5677</v>
       </c>
       <c r="Q16" t="n">
-        <v>-32.1911</v>
+        <v>-10.8753</v>
       </c>
       <c r="R16" t="n">
-        <v>33.931</v>
+        <v>6.3075</v>
       </c>
       <c r="S16" t="n">
-        <v>15.0473</v>
+        <v>-0.4325000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>7.013500000000001</v>
+        <v>-0.9301</v>
       </c>
       <c r="U16" t="n">
-        <v>8.034000000000001</v>
+        <v>0.4974000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-22.8139</v>
+        <v>1.1506</v>
       </c>
       <c r="W16" t="n">
-        <v>-2.9463</v>
+        <v>5.496</v>
       </c>
       <c r="X16" t="n">
-        <v>-19.8675</v>
+        <v>-4.3454</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>L. NIKKARINEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>-10.9468</v>
+        <v>-12.0481</v>
       </c>
       <c r="E17" t="n">
-        <v>-15.9743</v>
+        <v>-10.4394</v>
       </c>
       <c r="F17" t="n">
-        <v>5.027799999999999</v>
+        <v>-1.6086</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.6248</v>
+        <v>-7.7601</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.865</v>
+        <v>-5.4658</v>
       </c>
       <c r="I17" t="n">
-        <v>-14.7596</v>
+        <v>-2.2942</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8825</v>
+        <v>-5.552</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1838</v>
+        <v>-3.646</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.301499999999999</v>
+        <v>-1.9061</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.5073</v>
+        <v>-2.2082</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.048999999999999</v>
+        <v>-1.8199</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.4582</v>
+        <v>-0.3882000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>31.5384</v>
+        <v>1.9574</v>
       </c>
       <c r="Q17" t="n">
-        <v>-21.098</v>
+        <v>-4.350099999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>52.6367</v>
+        <v>6.3075</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1884</v>
+        <v>-4.3349</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.2491</v>
+        <v>-1.8627</v>
       </c>
       <c r="U17" t="n">
-        <v>3.4377</v>
+        <v>-2.4722</v>
       </c>
       <c r="V17" t="n">
-        <v>-26.049</v>
+        <v>-1.9109</v>
       </c>
       <c r="W17" t="n">
-        <v>4.4901</v>
+        <v>1.3252</v>
       </c>
       <c r="X17" t="n">
-        <v>-30.5392</v>
+        <v>-3.2361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>-12.8668</v>
+        <v>-12.1469</v>
       </c>
       <c r="E18" t="n">
-        <v>-11.3077</v>
+        <v>-19.3991</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5594</v>
+        <v>7.2525</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7373999999999998</v>
+        <v>-17.6248</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3160999999999999</v>
+        <v>-2.865</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0533</v>
+        <v>-14.7596</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5562999999999999</v>
+        <v>2.8825</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2038</v>
+        <v>5.1838</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7603000000000001</v>
+        <v>-2.301499999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1812</v>
+        <v>-20.5073</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1121</v>
+        <v>-8.048999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2934</v>
+        <v>-12.4582</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.1777</v>
+        <v>31.5384</v>
       </c>
       <c r="Q18" t="n">
-        <v>-8.700199999999999</v>
+        <v>-21.098</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>52.6367</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6443</v>
+        <v>-0.01159999999999984</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.507</v>
+        <v>-5.674</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1374</v>
+        <v>5.6622</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.3076</v>
+        <v>-26.049</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5443</v>
+        <v>4.4901</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7633</v>
+        <v>-30.5392</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. NIKKARINEN</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>-14.7727</v>
+        <v>-12.3321</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.8491</v>
+        <v>-10.6804</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9238</v>
+        <v>-1.6516</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.7601</v>
+        <v>-0.7373999999999998</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.4658</v>
+        <v>0.3160999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2942</v>
+        <v>-1.0533</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.552</v>
+        <v>-0.5562999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.646</v>
+        <v>0.2038</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9061</v>
+        <v>-0.7603000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2082</v>
+        <v>-0.1812</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8199</v>
+        <v>0.1121</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3882000000000001</v>
+        <v>-0.2934</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9574</v>
+        <v>-7.1777</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.350099999999999</v>
+        <v>-8.700199999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>6.3075</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-7.0596</v>
+        <v>-1.1094</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.2723</v>
+        <v>-0.8796</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.7873</v>
+        <v>-0.2298</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.9109</v>
+        <v>-3.3076</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>-0.5443</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.2361</v>
+        <v>-2.7633</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>-19.4637</v>
+        <v>-18.0894</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.195600000000001</v>
+        <v>-21.1653</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.2679</v>
+        <v>3.076</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3419</v>
+        <v>-2.6051</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.9808</v>
+        <v>-1.021599999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3613999999999998</v>
+        <v>-1.5829</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4312999999999999</v>
+        <v>14.7424</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4699</v>
+        <v>4.087499999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9009000000000001</v>
+        <v>10.6546</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.7732</v>
+        <v>-17.3471</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.511</v>
+        <v>-5.1092</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2625</v>
+        <v>-12.2379</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8699999999999998</v>
+        <v>1.7402</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.7425</v>
+        <v>-32.1911</v>
       </c>
       <c r="R20" t="n">
-        <v>5.8725</v>
+        <v>33.931</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9969</v>
+        <v>5.589399999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8401000000000001</v>
+        <v>-0.7699999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1571</v>
+        <v>6.3594</v>
       </c>
       <c r="V20" t="n">
-        <v>-12.2553</v>
+        <v>-22.8139</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9554999999999998</v>
+        <v>-2.9463</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.2108</v>
+        <v>-19.8675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
-        <v>-24.4174</v>
+        <v>-19.5284</v>
       </c>
       <c r="E21" t="n">
-        <v>-17.3997</v>
+        <v>-6.8411</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.0176</v>
+        <v>-12.6874</v>
       </c>
       <c r="G21" t="n">
-        <v>-26.1067</v>
+        <v>-4.3419</v>
       </c>
       <c r="H21" t="n">
-        <v>-12.9584</v>
+        <v>-3.9808</v>
       </c>
       <c r="I21" t="n">
-        <v>-13.1492</v>
+        <v>-0.3613999999999998</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4835999999999996</v>
+        <v>0.4312999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9493999999999998</v>
+        <v>-0.4699</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.433299999999999</v>
+        <v>0.9009000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-25.6234</v>
+        <v>-4.7732</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.9076</v>
+        <v>-3.511</v>
       </c>
       <c r="O21" t="n">
-        <v>-11.7155</v>
+        <v>-1.2625</v>
       </c>
       <c r="P21" t="n">
-        <v>9.1351</v>
+        <v>-0.8699999999999998</v>
       </c>
       <c r="Q21" t="n">
-        <v>-21.0981</v>
+        <v>-6.7425</v>
       </c>
       <c r="R21" t="n">
-        <v>30.2328</v>
+        <v>5.8725</v>
       </c>
       <c r="S21" t="n">
-        <v>-10.1079</v>
+        <v>-2.0616</v>
       </c>
       <c r="T21" t="n">
-        <v>-9.2242</v>
+        <v>-1.4852</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8836999999999997</v>
+        <v>-0.576</v>
       </c>
       <c r="V21" t="n">
-        <v>2.6623</v>
+        <v>-12.2553</v>
       </c>
       <c r="W21" t="n">
-        <v>13.4058</v>
+        <v>0.9554999999999998</v>
       </c>
       <c r="X21" t="n">
-        <v>-10.7435</v>
+        <v>-13.2108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>-24.4538</v>
+        <v>-19.9261</v>
       </c>
       <c r="E22" t="n">
-        <v>-16.7418</v>
+        <v>-15.5287</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.711700000000001</v>
+        <v>-4.3972</v>
       </c>
       <c r="G22" t="n">
-        <v>8.363099999999999</v>
+        <v>-26.1067</v>
       </c>
       <c r="H22" t="n">
-        <v>16.1998</v>
+        <v>-12.9584</v>
       </c>
       <c r="I22" t="n">
-        <v>-7.836299999999999</v>
+        <v>-13.1492</v>
       </c>
       <c r="J22" t="n">
-        <v>48.1573</v>
+        <v>-0.4835999999999996</v>
       </c>
       <c r="K22" t="n">
-        <v>32.1643</v>
+        <v>0.9493999999999998</v>
       </c>
       <c r="L22" t="n">
-        <v>15.9929</v>
+        <v>-1.433299999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-39.7941</v>
+        <v>-25.6234</v>
       </c>
       <c r="N22" t="n">
-        <v>-15.9649</v>
+        <v>-13.9076</v>
       </c>
       <c r="O22" t="n">
-        <v>-23.8295</v>
+        <v>-11.7155</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.652499999999999</v>
+        <v>9.1351</v>
       </c>
       <c r="Q22" t="n">
-        <v>-59.3791</v>
+        <v>-21.0981</v>
       </c>
       <c r="R22" t="n">
-        <v>58.7268</v>
+        <v>30.2328</v>
       </c>
       <c r="S22" t="n">
-        <v>-22.8093</v>
+        <v>-5.6164</v>
       </c>
       <c r="T22" t="n">
-        <v>-20.6529</v>
+        <v>-7.3531</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.1564</v>
+        <v>1.7362</v>
       </c>
       <c r="V22" t="n">
-        <v>-9.354699999999999</v>
+        <v>2.6623</v>
       </c>
       <c r="W22" t="n">
-        <v>15.133</v>
+        <v>13.4058</v>
       </c>
       <c r="X22" t="n">
-        <v>-24.4878</v>
+        <v>-10.7435</v>
       </c>
     </row>
     <row r="23">
@@ -2203,25 +2203,25 @@
         <v>32</v>
       </c>
       <c r="D23" t="n">
-        <v>-29.97180000000002</v>
+        <v>-3.426600000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-34.4577</v>
+        <v>-22.81329999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>4.485599999999999</v>
+        <v>19.38789999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>37.1063</v>
+        <v>37.10630000000002</v>
       </c>
       <c r="H23" t="n">
         <v>33.2916</v>
       </c>
       <c r="I23" t="n">
-        <v>3.815399999999999</v>
+        <v>3.815400000000004</v>
       </c>
       <c r="J23" t="n">
-        <v>317.0537</v>
+        <v>317.0536999999999</v>
       </c>
       <c r="K23" t="n">
         <v>142.8384</v>
@@ -2239,25 +2239,25 @@
         <v>-170.4003</v>
       </c>
       <c r="P23" t="n">
-        <v>-40.23949999999999</v>
+        <v>-40.23950000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-473.0756</v>
+        <v>-473.0756000000001</v>
       </c>
       <c r="R23" t="n">
         <v>432.8362</v>
       </c>
       <c r="S23" t="n">
-        <v>-24.317</v>
+        <v>2.229299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-66.7809</v>
+        <v>-55.1371</v>
       </c>
       <c r="U23" t="n">
-        <v>42.46470000000001</v>
+        <v>57.3659</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.523599999999997</v>
+        <v>-2.523600000000009</v>
       </c>
       <c r="W23" t="n">
         <v>188.3459</v>
